--- a/output/pdf_financials_xlsx/CCD.xlsx
+++ b/output/pdf_financials_xlsx/CCD.xlsx
@@ -2463,10 +2463,10 @@
         <v>0.160546</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.062158</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.023756</v>
       </c>
     </row>
     <row r="35">
@@ -2579,10 +2579,10 @@
         <v>0.160546</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.062158</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>0.023756</v>
       </c>
     </row>
     <row r="37">
@@ -3275,10 +3275,10 @@
         <v>0.033408</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.071477</v>
+        <v>0.009318999999999999</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.033112</v>
+        <v>0.009356</v>
       </c>
     </row>
     <row r="49">
@@ -8804,7 +8804,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -32977,7 +32977,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">

--- a/output/pdf_financials_xlsx/CCD.xlsx
+++ b/output/pdf_financials_xlsx/CCD.xlsx
@@ -6499,25 +6499,25 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>-0.002532</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>0.031613</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0</v>
+        <v>-0.013815</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>0</v>
+        <v>-0.10666</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>0</v>
+        <v>0.04407</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>0</v>
+        <v>0.031078</v>
       </c>
       <c r="H101" s="3" t="n">
-        <v>0</v>
+        <v>0.03453</v>
       </c>
       <c r="I101" s="3" t="n">
         <v>0</v>
@@ -7048,16 +7048,16 @@
         <v>0</v>
       </c>
       <c r="K110" s="3" t="n">
-        <v>0</v>
+        <v>0.007266</v>
       </c>
       <c r="L110" s="3" t="n">
-        <v>0</v>
+        <v>0.13208</v>
       </c>
       <c r="M110" s="3" t="n">
-        <v>0</v>
+        <v>0.025</v>
       </c>
       <c r="N110" s="3" t="n">
-        <v>0</v>
+        <v>0.108195</v>
       </c>
       <c r="O110" s="3" t="n">
         <v>0</v>
@@ -7082,13 +7082,13 @@
         <v>0</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.004769</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-0.005441</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>0</v>
+        <v>-0.001736</v>
       </c>
       <c r="F111" s="3" t="n">
         <v>0</v>
@@ -7097,7 +7097,7 @@
         <v>0</v>
       </c>
       <c r="H111" s="3" t="n">
-        <v>0</v>
+        <v>-0.002404</v>
       </c>
       <c r="I111" s="3" t="n">
         <v>0</v>
@@ -8452,13 +8452,13 @@
         <v>0</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.004769</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.005441</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>0</v>
+        <v>-0.001736</v>
       </c>
       <c r="F134" s="3" t="n">
         <v>0</v>
@@ -8467,7 +8467,7 @@
         <v>0</v>
       </c>
       <c r="H134" s="3" t="n">
-        <v>0</v>
+        <v>-0.002404</v>
       </c>
       <c r="I134" s="3" t="n">
         <v>0</v>
@@ -8510,7 +8510,7 @@
         <v>-0.311083</v>
       </c>
       <c r="C135" s="3" t="n">
-        <v>-0.323501</v>
+        <v>-0.32827</v>
       </c>
       <c r="D135" s="1" t="inlineStr">
         <is>
@@ -8518,7 +8518,7 @@
         </is>
       </c>
       <c r="E135" s="3" t="n">
-        <v>-0.633265</v>
+        <v>-0.635001</v>
       </c>
       <c r="F135" s="3" t="n">
         <v>-0.600631</v>
@@ -8527,7 +8527,7 @@
         <v>-0.36374</v>
       </c>
       <c r="H135" s="3" t="n">
-        <v>-0.022501</v>
+        <v>-0.024905</v>
       </c>
       <c r="I135" s="3" t="n">
         <v>-0.661989</v>
@@ -20590,7 +20590,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr"/>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E123" t="inlineStr">
         <is>
           <t>-</t>
@@ -21390,7 +21394,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr"/>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E131" t="inlineStr">
         <is>
           <t>-</t>
@@ -27697,7 +27705,11 @@
           <t>Purchase of Equipment</t>
         </is>
       </c>
-      <c r="D194" t="inlineStr"/>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E194" t="inlineStr">
         <is>
           <t>-</t>
@@ -28859,7 +28871,11 @@
           <t>GST recoverable</t>
         </is>
       </c>
-      <c r="D206" t="inlineStr"/>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E206" t="inlineStr">
         <is>
           <t>-</t>
@@ -31078,7 +31094,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D229" t="inlineStr"/>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E229" t="inlineStr">
         <is>
           <t>-</t>
@@ -32080,7 +32100,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D239" t="inlineStr"/>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E239" s="5" t="n">
         <v>-0.002532</v>
       </c>
